--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759996</v>
       </c>
       <c r="B2" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759995</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136759994</v>
       </c>
       <c r="B5" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38286-2026 artfynd.xlsx
+++ b/artfynd/A 38286-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136759993</v>
       </c>
       <c r="B4" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136759992</v>
       </c>
       <c r="B6" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
